--- a/Analysis/cluster_bootstrap_ci.xlsx
+++ b/Analysis/cluster_bootstrap_ci.xlsx
@@ -512,31 +512,31 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.144</v>
+        <v>0.1248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0537</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2208</v>
+        <v>0.1959</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1556</v>
+        <v>0.1422</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1157</v>
+        <v>0.1002</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1774</v>
+        <v>0.1494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0617</v>
+        <v>0.0492</v>
       </c>
       <c r="M2" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0407</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="3">
@@ -562,31 +562,31 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1761</v>
+        <v>0.1788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0844</v>
+        <v>0.0728</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2656</v>
+        <v>0.2821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1812</v>
+        <v>0.2092</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1651</v>
+        <v>0.1631</v>
       </c>
       <c r="K3" t="n">
-        <v>0.187</v>
+        <v>0.1938</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0219</v>
+        <v>0.0308</v>
       </c>
       <c r="M3" t="n">
-        <v>8.279999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0143</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="4">
@@ -612,31 +612,31 @@
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0407</v>
+        <v>0.0325</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0263</v>
+        <v>-0.0352</v>
       </c>
       <c r="H4" t="n">
-        <v>0.107</v>
+        <v>0.1022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1333</v>
+        <v>0.1374</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0072</v>
+        <v>0.0133</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0776</v>
+        <v>0.0503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0704</v>
+        <v>0.0369</v>
       </c>
       <c r="M4" t="n">
-        <v>1.89</v>
+        <v>3.72</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0452</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="5">
@@ -662,31 +662,31 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0.0055</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0497</v>
+        <v>-0.0468</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0708</v>
+        <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1206</v>
+        <v>0.105</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.026</v>
+        <v>-0.0229</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0326</v>
+        <v>0.0338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0586</v>
+        <v>0.0568</v>
       </c>
       <c r="M5" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0385</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="6">
@@ -712,31 +712,31 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3067</v>
+        <v>0.253</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2349</v>
+        <v>0.1832</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3757</v>
+        <v>0.3221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1409</v>
+        <v>0.1388</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2793</v>
+        <v>0.2232</v>
       </c>
       <c r="K6" t="n">
-        <v>0.334</v>
+        <v>0.2824</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0547</v>
+        <v>0.0591</v>
       </c>
       <c r="M6" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0356</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="7">
@@ -762,31 +762,31 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3099</v>
+        <v>0.2985</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2158</v>
+        <v>0.202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4009</v>
+        <v>0.3915</v>
       </c>
       <c r="I7" t="n">
-        <v>0.185</v>
+        <v>0.1894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2941</v>
+        <v>0.2923</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3236</v>
+        <v>0.3046</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0295</v>
+        <v>0.0123</v>
       </c>
       <c r="M7" t="n">
-        <v>6.26</v>
+        <v>15.39</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0187</v>
+        <v>0.008200000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -812,31 +812,31 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2725</v>
+        <v>0.2342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1986</v>
+        <v>0.1549</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3456</v>
+        <v>0.3094</v>
       </c>
       <c r="I8" t="n">
-        <v>0.147</v>
+        <v>0.1545</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2458</v>
+        <v>0.2041</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3053</v>
+        <v>0.2677</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0595</v>
+        <v>0.0636</v>
       </c>
       <c r="M8" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0398</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="9">
@@ -862,31 +862,31 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2082</v>
+        <v>0.1474</v>
       </c>
       <c r="G9" t="n">
-        <v>0.148</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2684</v>
+        <v>0.2096</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1203</v>
+        <v>0.1265</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1754</v>
+        <v>0.1262</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2315</v>
+        <v>0.1679</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0561</v>
+        <v>0.0417</v>
       </c>
       <c r="M9" t="n">
-        <v>2.15</v>
+        <v>3.03</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0366</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="10">
@@ -912,31 +912,31 @@
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8973</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8085</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9344</v>
+        <v>0.8995</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0779</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.893</v>
+        <v>0.8489</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9015</v>
+        <v>0.8663</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0174</v>
       </c>
       <c r="M10" t="n">
-        <v>9.119999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0056</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="11">
@@ -962,31 +962,31 @@
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9234</v>
+        <v>0.8913</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8844</v>
+        <v>0.8448</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9562</v>
+        <v>0.9316</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0718</v>
+        <v>0.0868</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9221</v>
+        <v>0.8872</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9248</v>
+        <v>0.8954</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0027</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>26.25</v>
+        <v>10.58</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0019</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="12">
@@ -1006,37 +1006,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8974</v>
+        <v>0.8048</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8599</v>
+        <v>0.76</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9314</v>
+        <v>0.8462</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8913</v>
+        <v>0.7945</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9029</v>
+        <v>0.8144</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0117</v>
+        <v>0.0198</v>
       </c>
       <c r="M12" t="n">
-        <v>6.13</v>
+        <v>4.34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0072</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="13">
@@ -1062,31 +1062,31 @@
         <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8316</v>
+        <v>0.7826</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9233</v>
+        <v>0.8844</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0917</v>
+        <v>0.1019</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8686</v>
+        <v>0.827</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8902</v>
+        <v>0.8455</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0216</v>
+        <v>0.0185</v>
       </c>
       <c r="M13" t="n">
-        <v>4.25</v>
+        <v>5.52</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0133</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="14">
@@ -1112,31 +1112,31 @@
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2314</v>
+        <v>0.2232</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2224</v>
+        <v>0.2124</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2409</v>
+        <v>0.2341</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0185</v>
+        <v>0.0217</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2296</v>
+        <v>0.2208</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2336</v>
+        <v>0.2253</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0039</v>
+        <v>0.0045</v>
       </c>
       <c r="M14" t="n">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="15">
@@ -1162,31 +1162,31 @@
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.219</v>
+        <v>0.2071</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2067</v>
+        <v>0.1972</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2319</v>
+        <v>0.2177</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0252</v>
+        <v>0.0206</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2176</v>
+        <v>0.2065</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2202</v>
+        <v>0.2078</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0026</v>
+        <v>0.0013</v>
       </c>
       <c r="M15" t="n">
-        <v>9.789999999999999</v>
+        <v>15.71</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0016</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="16">
@@ -1212,31 +1212,31 @@
         <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2411</v>
+        <v>0.2465</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2299</v>
+        <v>0.2356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2526</v>
+        <v>0.2575</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0226</v>
+        <v>0.0219</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2396</v>
+        <v>0.2442</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2425</v>
+        <v>0.2485</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0029</v>
+        <v>0.0043</v>
       </c>
       <c r="M16" t="n">
-        <v>7.79</v>
+        <v>5.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0019</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="17">
@@ -1262,31 +1262,31 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2349</v>
+        <v>0.2392</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2248</v>
+        <v>0.2287</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2452</v>
+        <v>0.2497</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0204</v>
+        <v>0.021</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2336</v>
+        <v>0.2375</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2364</v>
+        <v>0.241</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0028</v>
+        <v>0.0035</v>
       </c>
       <c r="M17" t="n">
-        <v>7.29</v>
+        <v>6.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0018</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="18">
@@ -1312,31 +1312,31 @@
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1677</v>
+        <v>0.1702</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1554</v>
+        <v>0.1575</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1809</v>
+        <v>0.1839</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0255</v>
+        <v>0.0263</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1671</v>
+        <v>0.1689</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1682</v>
+        <v>0.1714</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0011</v>
+        <v>0.0024</v>
       </c>
       <c r="M18" t="n">
-        <v>23.97</v>
+        <v>10.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0007</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="19">
@@ -1362,31 +1362,31 @@
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1584</v>
+        <v>0.147</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1461</v>
+        <v>0.1359</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1711</v>
+        <v>0.1587</v>
       </c>
       <c r="I19" t="n">
-        <v>0.025</v>
+        <v>0.0228</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1575</v>
+        <v>0.1465</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1592</v>
+        <v>0.1477</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0016</v>
+        <v>0.0012</v>
       </c>
       <c r="M19" t="n">
-        <v>15.35</v>
+        <v>19.68</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0011</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="20">
@@ -1412,31 +1412,31 @@
         <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.169</v>
+        <v>0.1792</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1577</v>
+        <v>0.1676</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1809</v>
+        <v>0.1911</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0232</v>
+        <v>0.0235</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1673</v>
+        <v>0.1779</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1708</v>
+        <v>0.1803</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0035</v>
+        <v>0.0024</v>
       </c>
       <c r="M20" t="n">
-        <v>6.7</v>
+        <v>9.98</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0022</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="21">
@@ -1462,31 +1462,31 @@
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1935</v>
+        <v>0.1985</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1819</v>
+        <v>0.1865</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2055</v>
+        <v>0.2106</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0236</v>
+        <v>0.024</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1908</v>
+        <v>0.1954</v>
       </c>
       <c r="K21" t="n">
-        <v>0.196</v>
+        <v>0.2019</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0053</v>
+        <v>0.0065</v>
       </c>
       <c r="M21" t="n">
-        <v>4.49</v>
+        <v>3.69</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0034</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="22">
@@ -1512,31 +1512,31 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0448</v>
+        <v>0.0548</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0396</v>
+        <v>0.0474</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0506</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.011</v>
+        <v>0.0154</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0415</v>
+        <v>0.0539</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0476</v>
+        <v>0.0559</v>
       </c>
       <c r="L22" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="M22" t="n">
-        <v>1.83</v>
+        <v>7.71</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0038</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="23">
@@ -1562,31 +1562,31 @@
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0477</v>
+        <v>0.0483</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0411</v>
+        <v>0.0426</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0547</v>
+        <v>0.0545</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0136</v>
+        <v>0.0119</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0472</v>
+        <v>0.0473</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0483</v>
+        <v>0.0494</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0011</v>
+        <v>0.0021</v>
       </c>
       <c r="M23" t="n">
-        <v>12.28</v>
+        <v>5.68</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="24">
@@ -1606,37 +1606,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0519</v>
+        <v>0.0793</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0461</v>
+        <v>0.0699</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0581</v>
+        <v>0.0892</v>
       </c>
       <c r="I24" t="n">
-        <v>0.012</v>
+        <v>0.0194</v>
       </c>
       <c r="J24" t="n">
-        <v>0.051</v>
+        <v>0.0774</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0532</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0022</v>
+        <v>0.0037</v>
       </c>
       <c r="M24" t="n">
-        <v>5.57</v>
+        <v>5.22</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0015</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="25">
@@ -1662,31 +1662,31 @@
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0718</v>
+        <v>0.0745</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0612</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0832</v>
+        <v>0.0856</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0219</v>
+        <v>0.0214</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0702</v>
+        <v>0.0726</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0731</v>
+        <v>0.0762</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0028</v>
+        <v>0.0037</v>
       </c>
       <c r="M25" t="n">
-        <v>7.81</v>
+        <v>5.87</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0018</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="26">
@@ -1712,31 +1712,31 @@
         <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3668</v>
+        <v>0.3908</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3175</v>
+        <v>0.3436</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4166</v>
+        <v>0.4379</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0944</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3471</v>
+        <v>0.3682</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3948</v>
+        <v>0.4133</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0477</v>
+        <v>0.0451</v>
       </c>
       <c r="M26" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0309</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="27">
@@ -1762,31 +1762,31 @@
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3621</v>
+        <v>0.3979</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3005</v>
+        <v>0.3323</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4256</v>
+        <v>0.4646</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1251</v>
+        <v>0.1323</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3508</v>
+        <v>0.3918</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3744</v>
+        <v>0.4041</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0236</v>
+        <v>0.0123</v>
       </c>
       <c r="M27" t="n">
-        <v>5.3</v>
+        <v>10.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0148</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="28">
@@ -1812,31 +1812,31 @@
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3333</v>
+        <v>0.3405</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2903</v>
+        <v>0.2985</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3774</v>
+        <v>0.3846</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0872</v>
+        <v>0.0862</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3149</v>
+        <v>0.3241</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3518</v>
+        <v>0.3579</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0369</v>
+        <v>0.0338</v>
       </c>
       <c r="M28" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0241</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="29">
@@ -1862,31 +1862,31 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3001</v>
+        <v>0.3077</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2595</v>
+        <v>0.2677</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3419</v>
+        <v>0.3487</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0824</v>
+        <v>0.081</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2772</v>
+        <v>0.2862</v>
       </c>
       <c r="K29" t="n">
-        <v>0.323</v>
+        <v>0.3251</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0296</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="30">
@@ -1912,31 +1912,31 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5354</v>
+        <v>0.4831</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4831</v>
+        <v>0.4318</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5856</v>
+        <v>0.5344</v>
       </c>
       <c r="I30" t="n">
         <v>0.1026</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5097</v>
+        <v>0.4667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.4933</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0513</v>
+        <v>0.0267</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>0.033</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="31">
@@ -1962,31 +1962,31 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4871</v>
+        <v>0.4749</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4225</v>
+        <v>0.4092</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5526</v>
+        <v>0.5395</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1301</v>
+        <v>0.1303</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4716</v>
+        <v>0.4646</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5026</v>
+        <v>0.4831</v>
       </c>
       <c r="L31" t="n">
-        <v>0.031</v>
+        <v>0.0185</v>
       </c>
       <c r="M31" t="n">
-        <v>4.19</v>
+        <v>7.06</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0199</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="32">
@@ -2012,31 +2012,31 @@
         <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4738</v>
+        <v>0.4646</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4215</v>
+        <v>0.4133</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5262</v>
+        <v>0.5159</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1046</v>
+        <v>0.1026</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4564</v>
+        <v>0.4308</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4882</v>
+        <v>0.4985</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0318</v>
+        <v>0.0677</v>
       </c>
       <c r="M32" t="n">
-        <v>3.29</v>
+        <v>1.52</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0207</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="33">
@@ -2062,31 +2062,31 @@
         <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4656</v>
+        <v>0.439</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4215</v>
+        <v>0.3918</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5087</v>
+        <v>0.4862</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0872</v>
+        <v>0.0944</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4533</v>
+        <v>0.4185</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4779</v>
+        <v>0.4544</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0246</v>
+        <v>0.0359</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>2.63</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0156</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="34">
@@ -2112,31 +2112,31 @@
         <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9076</v>
+        <v>0.8862</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8694</v>
+        <v>0.8441</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9415</v>
+        <v>0.9241</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0721</v>
+        <v>0.08</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9003</v>
+        <v>0.879</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9159</v>
+        <v>0.8933</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0156</v>
+        <v>0.0144</v>
       </c>
       <c r="M34" t="n">
-        <v>4.62</v>
+        <v>5.57</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0097</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="35">
@@ -2162,31 +2162,31 @@
         <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9313</v>
+        <v>0.9015</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8933</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9641</v>
+        <v>0.9405</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0708</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9292</v>
+        <v>0.8985</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9333</v>
+        <v>0.9046</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0041</v>
+        <v>0.0062</v>
       </c>
       <c r="M35" t="n">
-        <v>17.25</v>
+        <v>13.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0028</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="36">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E36" t="n">
         <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9173</v>
+        <v>0.8246</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8828</v>
+        <v>0.7815</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9479</v>
+        <v>0.8646</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9131</v>
+        <v>0.8174</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9234</v>
+        <v>0.8318</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0104</v>
+        <v>0.0144</v>
       </c>
       <c r="M36" t="n">
-        <v>6.29</v>
+        <v>5.79</v>
       </c>
       <c r="N36" t="n">
-        <v>0.007</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="37">
@@ -2262,31 +2262,31 @@
         <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8972</v>
+        <v>0.8646</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8571</v>
+        <v>0.8205</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9342</v>
+        <v>0.9067</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0771</v>
+        <v>0.0862</v>
       </c>
       <c r="J37" t="n">
-        <v>0.89</v>
+        <v>0.8544</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9074</v>
+        <v>0.8718</v>
       </c>
       <c r="L37" t="n">
         <v>0.0174</v>
       </c>
       <c r="M37" t="n">
-        <v>4.43</v>
+        <v>4.94</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="38">
@@ -2312,31 +2312,31 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7221</v>
+        <v>0.7292</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6851</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7683</v>
+        <v>0.7713</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0954</v>
+        <v>0.0862</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7104</v>
+        <v>0.7097</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7378</v>
+        <v>0.7467</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0274</v>
+        <v>0.0369</v>
       </c>
       <c r="M38" t="n">
-        <v>3.49</v>
+        <v>2.33</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0178</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="39">
@@ -2362,31 +2362,31 @@
         <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6974</v>
+        <v>0.7026</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6359</v>
+        <v>0.639</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7559</v>
+        <v>0.7651</v>
       </c>
       <c r="I39" t="n">
-        <v>0.12</v>
+        <v>0.1262</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6841</v>
+        <v>0.6954</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7087</v>
+        <v>0.7097</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0246</v>
+        <v>0.0144</v>
       </c>
       <c r="M39" t="n">
-        <v>4.87</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0162</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2412,31 +2412,31 @@
         <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6646</v>
+        <v>0.6656</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7077</v>
+        <v>0.7087</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0882</v>
+        <v>0.0872</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6451</v>
+        <v>0.64</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6862</v>
+        <v>0.6892</v>
       </c>
       <c r="L40" t="n">
-        <v>0.041</v>
+        <v>0.0492</v>
       </c>
       <c r="M40" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0263</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="41">
@@ -2462,31 +2462,31 @@
         <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6773</v>
+        <v>0.6646</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6385</v>
+        <v>0.6267</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7161</v>
+        <v>0.7005</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0776</v>
+        <v>0.0738</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6571</v>
+        <v>0.6451</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6958</v>
+        <v>0.6841</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0387</v>
+        <v>0.039</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="N41" t="n">
-        <v>0.025</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="42">
@@ -2512,31 +2512,31 @@
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8113</v>
+        <v>0.8164</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7703</v>
+        <v>0.7795</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.08</v>
+        <v>0.0718</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8318</v>
+        <v>0.8226</v>
       </c>
       <c r="L42" t="n">
-        <v>0.04</v>
+        <v>0.0144</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0239</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -2562,31 +2562,31 @@
         <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7958</v>
+        <v>0.7713</v>
       </c>
       <c r="G43" t="n">
-        <v>0.741</v>
+        <v>0.7149</v>
       </c>
       <c r="H43" t="n">
-        <v>0.847</v>
+        <v>0.8246</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1061</v>
+        <v>0.1097</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7927</v>
+        <v>0.7672</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8004</v>
+        <v>0.7764</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0077</v>
+        <v>0.0092</v>
       </c>
       <c r="M43" t="n">
-        <v>13.86</v>
+        <v>11.89</v>
       </c>
       <c r="N43" t="n">
-        <v>0.005</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="44">
@@ -2612,31 +2612,31 @@
         <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7651</v>
+        <v>0.7631</v>
       </c>
       <c r="G44" t="n">
-        <v>0.719</v>
+        <v>0.7179</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8092</v>
+        <v>0.8062</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7436</v>
+        <v>0.7508</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7856</v>
+        <v>0.7764</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0421</v>
+        <v>0.0256</v>
       </c>
       <c r="M44" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="N44" t="n">
-        <v>0.027</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="45">
@@ -2662,31 +2662,31 @@
         <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7805</v>
+        <v>0.7395</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7456</v>
+        <v>0.6974</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8144</v>
+        <v>0.7795</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0687</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7579</v>
+        <v>0.7251</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8051</v>
+        <v>0.7538</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0472</v>
+        <v>0.0287</v>
       </c>
       <c r="M45" t="n">
-        <v>1.46</v>
+        <v>2.86</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0302</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="46">
@@ -2712,31 +2712,31 @@
         <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9774</v>
+        <v>0.9651</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9567</v>
+        <v>0.9405</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9949</v>
+        <v>0.9856</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0381</v>
+        <v>0.0451</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9621</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9815</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0072</v>
+        <v>0.0062</v>
       </c>
       <c r="M46" t="n">
-        <v>5.27</v>
+        <v>7.33</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0046</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="47">
@@ -2762,22 +2762,22 @@
         <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9641</v>
+        <v>0.959</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="I47" t="n">
         <v>0.0359</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2804,37 +2804,37 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E48" t="n">
         <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9813</v>
+        <v>0.8933</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9647</v>
+        <v>0.8595</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9942</v>
+        <v>0.9241</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0294</v>
+        <v>0.0646</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9752</v>
+        <v>0.8882</v>
       </c>
       <c r="K48" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.8985</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0132</v>
+        <v>0.0103</v>
       </c>
       <c r="M48" t="n">
-        <v>2.24</v>
+        <v>6.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="49">
@@ -2860,31 +2860,31 @@
         <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9692</v>
+        <v>0.96</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9455</v>
+        <v>0.9354</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9887</v>
+        <v>0.9815</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0432</v>
+        <v>0.0462</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9631</v>
+        <v>0.9549</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9651</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0122</v>
+        <v>0.0103</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0072</v>
+        <v>0.0067</v>
       </c>
     </row>
   </sheetData>
@@ -2963,13 +2963,13 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1627</v>
+        <v>0.1282</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0699</v>
+        <v>0.0492</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2562</v>
+        <v>0.2072</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -2995,13 +2995,13 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0523</v>
+        <v>-0.0412</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -3027,13 +3027,13 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1686</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1012</v>
+        <v>0.0297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2338</v>
+        <v>0.1549</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -3059,13 +3059,13 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0892</v>
+        <v>0.0872</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0315</v>
+        <v>0.0379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.147</v>
+        <v>0.1364</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -3091,13 +3091,13 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5907</v>
+        <v>0.6034</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5108</v>
+        <v>0.5258</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6715</v>
+        <v>0.6814</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -3123,13 +3123,13 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1229</v>
+        <v>-0.1154</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1362</v>
+        <v>-0.1299</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1102</v>
+        <v>-0.1016</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -3155,13 +3155,13 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3722</v>
+        <v>0.4031</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3126</v>
+        <v>0.3426</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4344</v>
+        <v>0.4636</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -3187,13 +3187,13 @@
         <v>195</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1661</v>
+        <v>0.1487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.121</v>
+        <v>0.1087</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2123</v>
+        <v>0.1897</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -3219,13 +3219,13 @@
         <v>195</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7533</v>
+        <v>0.7316</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6662</v>
+        <v>0.6462</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8418</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -3251,13 +3251,13 @@
         <v>195</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1866</v>
+        <v>-0.1684</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1971</v>
+        <v>-0.1818</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1761</v>
+        <v>-0.1548</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -3283,13 +3283,13 @@
         <v>195</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.4954</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4765</v>
+        <v>0.4338</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6037</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -3315,13 +3315,13 @@
         <v>195</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2553</v>
+        <v>0.2359</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2033</v>
+        <v>0.1877</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3091</v>
+        <v>0.2841</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -3347,13 +3347,13 @@
         <v>195</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1338</v>
+        <v>0.1197</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0544</v>
+        <v>0.0526</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2155</v>
+        <v>0.1928</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -3379,13 +3379,13 @@
         <v>195</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0607</v>
+        <v>-0.0601</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0501</v>
+        <v>-0.0513</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -3411,13 +3411,13 @@
         <v>195</v>
       </c>
       <c r="E16" t="n">
-        <v>0.125</v>
+        <v>0.0769</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0524</v>
+        <v>0.0195</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1996</v>
+        <v>0.1354</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -3443,13 +3443,13 @@
         <v>195</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0984</v>
+        <v>0.0687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0515</v>
+        <v>0.0267</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1478</v>
+        <v>0.1138</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -3475,13 +3475,13 @@
         <v>195</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6135</v>
+        <v>0.5928</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5143</v>
+        <v>0.4882</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7143</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -3507,13 +3507,13 @@
         <v>195</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1107</v>
+        <v>-0.0987</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1245</v>
+        <v>-0.1109</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0975</v>
+        <v>-0.0867</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -3539,13 +3539,13 @@
         <v>195</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4442</v>
+        <v>0.4267</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3704</v>
+        <v>0.3508</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5165</v>
+        <v>0.5026</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -3571,13 +3571,13 @@
         <v>195</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1888</v>
+        <v>0.2082</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1334</v>
+        <v>0.1507</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2477</v>
+        <v>0.2677</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -3603,13 +3603,13 @@
         <v>195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7474</v>
+        <v>0.7125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6544</v>
+        <v>0.6044</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8417</v>
+        <v>0.8246</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -3635,13 +3635,13 @@
         <v>195</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1713</v>
+        <v>-0.1588</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1848</v>
+        <v>-0.1698</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1584</v>
+        <v>-0.1482</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -3667,13 +3667,13 @@
         <v>195</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5692</v>
+        <v>0.5036</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5026</v>
+        <v>0.4267</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6349</v>
+        <v>0.5805</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -3699,13 +3699,13 @@
         <v>195</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2872</v>
+        <v>0.2769</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2277</v>
+        <v>0.2133</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3497</v>
+        <v>0.3415</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -3731,13 +3731,13 @@
         <v>195</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2318</v>
+        <v>0.2017</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1525</v>
+        <v>0.1217</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3104</v>
+        <v>0.2797</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -3763,13 +3763,13 @@
         <v>195</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0721</v>
+        <v>-0.0673</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0788</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0597</v>
+        <v>-0.0559</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -3795,13 +3795,13 @@
         <v>195</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1405</v>
+        <v>0.1241</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08</v>
+        <v>0.0677</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1979</v>
+        <v>0.1785</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -3827,13 +3827,13 @@
         <v>195</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1005</v>
+        <v>0.0974</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0472</v>
+        <v>0.0462</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1518</v>
+        <v>0.1477</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E30" t="n">
-        <v>0.628</v>
+        <v>0.5706</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5474</v>
+        <v>0.4814</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7105</v>
+        <v>0.6615</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -3888,16 +3888,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1177</v>
+        <v>-0.0999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1302</v>
+        <v>-0.1152</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.106</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -3920,16 +3920,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4451</v>
+        <v>0.36</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3849</v>
+        <v>0.2933</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5038</v>
+        <v>0.4246</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -3952,16 +3952,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2173</v>
+        <v>0.1303</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1713</v>
+        <v>0.0728</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2662</v>
+        <v>0.1877</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -3984,16 +3984,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8569</v>
+        <v>0.7723</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7844</v>
+        <v>0.6906</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9283</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -4016,16 +4016,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1894</v>
+        <v>-0.1672</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2023</v>
+        <v>-0.1832</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1763</v>
+        <v>-0.1506</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -4048,16 +4048,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5843</v>
+        <v>0.4841</v>
       </c>
       <c r="F36" t="n">
-        <v>0.532</v>
+        <v>0.4205</v>
       </c>
       <c r="G36" t="n">
-        <v>0.636</v>
+        <v>0.5456</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -4080,16 +4080,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3173</v>
+        <v>0.2277</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2737</v>
+        <v>0.1713</v>
       </c>
       <c r="G37" t="n">
-        <v>0.362</v>
+        <v>0.2831</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -4115,13 +4115,13 @@
         <v>195</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1982</v>
+        <v>0.1419</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1062</v>
+        <v>0.0526</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2889</v>
+        <v>0.2308</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -4147,13 +4147,13 @@
         <v>195</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0413</v>
+        <v>-0.0407</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0521</v>
+        <v>-0.0519</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0305</v>
+        <v>-0.0294</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -4179,13 +4179,13 @@
         <v>195</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1655</v>
+        <v>0.1313</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1018</v>
+        <v>0.0667</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2284</v>
+        <v>0.1959</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -4211,13 +4211,13 @@
         <v>195</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1032</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0462</v>
+        <v>0.0164</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1591</v>
+        <v>0.1323</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -4243,13 +4243,13 @@
         <v>195</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6885</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5985</v>
+        <v>0.6099</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7423</v>
+        <v>0.7644</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -4275,13 +4275,13 @@
         <v>195</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1217</v>
+        <v>-0.124</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.138</v>
+        <v>-0.1402</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.1053</v>
+        <v>-0.1074</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -4307,13 +4307,13 @@
         <v>195</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4316</v>
+        <v>0.4256</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3741</v>
+        <v>0.3651</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4882</v>
+        <v>0.4872</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -4339,13 +4339,13 @@
         <v>195</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1887</v>
+        <v>0.2205</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1487</v>
+        <v>0.1744</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2276</v>
+        <v>0.2677</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -4371,13 +4371,13 @@
         <v>195</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8701</v>
+        <v>0.8304</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7973</v>
+        <v>0.7614</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9405</v>
+        <v>0.8991</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -4403,13 +4403,13 @@
         <v>195</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1631</v>
+        <v>-0.1647</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1748</v>
+        <v>-0.177</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1513</v>
+        <v>-0.152</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -4435,13 +4435,13 @@
         <v>195</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5971</v>
+        <v>0.5569</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5419</v>
+        <v>0.4995</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6505</v>
+        <v>0.6133</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -4467,13 +4467,13 @@
         <v>195</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2919</v>
+        <v>0.2954</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2462</v>
+        <v>0.2544</v>
       </c>
       <c r="G49" t="n">
-        <v>0.337</v>
+        <v>0.3364</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
